--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,7 +53,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -67,6 +67,12 @@
       <color rgb="002563EB"/>
       <sz val="9"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -108,7 +114,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -132,7 +138,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -143,6 +149,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -182,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -208,32 +219,35 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -619,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 29/06/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 14 bandi verificati + 5 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 14 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -728,14 +742,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>1gg</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>SCAD.</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>IN SCADENZA</t>
+          <t>CHIUSO</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -790,14 +804,14 @@
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>32gg</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>25gg</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -810,7 +824,7 @@
           <t>Solo chi ha versato acconto &gt;=20% entro 31/12/2025.</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -852,14 +866,14 @@
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>32gg</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>25gg</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -916,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>93gg</t>
+          <t>86gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -934,7 +948,7 @@
           <t>Solo province Milano, Monza Brianza e Lodi.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -978,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>158gg</t>
+          <t>151gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1058,7 +1072,7 @@
           <t>Sportello PMI aprira seconda meta 2026.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1102,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1164,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1182,7 +1196,7 @@
           <t>Include AI, cloud, Industry 4.0.</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1226,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1288,7 +1302,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1302,7 +1316,7 @@
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1346,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1408,7 +1422,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1422,7 +1436,7 @@
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1466,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>366gg</t>
+          <t>359gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1528,7 +1542,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>550gg</t>
+          <t>543gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1546,7 +1560,7 @@
           <t>Rifinanziata con 650M euro per 2026-2027. Sportello continuo.</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1555,7 +1569,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Contributo integrativo Regionale sulla spesa assicurativa agevolata “Sma...</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1570,7 +1584,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1585,12 +1599,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>93gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1598,7 +1612,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1617,7 +1631,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1652,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1660,7 +1674,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1670,7 +1684,7 @@
           <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1679,7 +1693,7 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1714,7 +1728,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>185gg</t>
+          <t>178gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1722,7 +1736,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1738,143 +1752,19 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ricerca e Innovazione</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>185gg</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Interventi speciali a favore della montagna di cui alla DGR 7391/2022</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>185gg</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  19 bandi | 18 aperti | 1 in scadenza | 14 verificati manualmente | Aggiornato: 29/06/2026</t>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17 bandi | 14 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 06/07/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L22"/>
+  <autoFilter ref="A3:L20"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A23:L23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId1"/>
@@ -1894,8 +1784,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1907,7 +1795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1920,66 +1808,93 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 29/06/2026</t>
+          <t>DASHBOARD — 06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>BANDI IN SCADENZA ENTRO 30 GIORNI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>BANDO</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ENTE</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>SCADENZA</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>GIORNI</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Rafforza &amp; Innova 2025</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Regione Lombardia / Finlombarda</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>1 gg</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Credito d'Imposta Beni Strumentali 4.0</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>MIMIT / Agenzia delle Entrate</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>25 gg</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Voucher Fiere e Mostre CCIAA Toscana NW 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Camera di Commercio Toscana Nord-Ovest</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>25 gg</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Apri bando</t>
         </is>
@@ -1992,6 +1907,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2012,283 +1928,283 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>LEGENDA E FONTI MONITORATE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>COLONNA FONTE</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr"/>
-      <c r="C3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr"/>
+      <c r="C3" s="19" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>OK (verde)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Bando verificato manualmente su fonte ufficiale — affidabile</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr"/>
+      <c r="C4" s="19" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>AUTO (viola)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Trovato automaticamente via scraping — verificare prima dell'uso con clienti</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr"/>
+      <c r="C5" s="19" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="18" t="inlineStr"/>
-      <c r="B6" s="18" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr"/>
+      <c r="A6" s="19" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>COLONNA STATO</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>APERTO (verde)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Bando con scadenza futura &gt; 30 giorni</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>IN SCADENZA (giallo)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Scadenza entro 30 giorni — agire subito</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>CHIUSO (rosso)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Bando scaduto (mostrato per 60 giorni poi rimosso)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="18" t="inlineStr"/>
-      <c r="C11" s="18" t="inlineStr"/>
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>FONTI MONITORATE</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr"/>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>FREQ.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Regione Toscana</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>regione.toscana.it / bandi FESR 2021-2027</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>bandi.regione.lombardia.it</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>MIMIT</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>mimit.gov.it/it/incentivi</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>SIMEST</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>simest.it (tutte le linee Fondo 394)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>CCIAA Toscana NW</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>tno.camcom.it/bandi (Lucca-Massa-Pisa)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>CCIAA Arezzo-Siena</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>as.camcom.it</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CCIAA Firenze</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>fi.camcom.gov.it</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>EUIPO</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>euipo.europa.eu/sme-fund/2026</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>incentivi.gov.it</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Catalogo MIMIT (aggregatore ufficiale)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Agenzia Entrate</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Crediti d'imposta Formazione e Beni 4.0</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -633,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 06/07/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 14 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 14 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>25gg</t>
+          <t>18gg</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>25gg</t>
+          <t>18gg</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>86gg</t>
+          <t>79gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>151gg</t>
+          <t>144gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>359gg</t>
+          <t>352gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>543gg</t>
+          <t>536gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>178gg</t>
+          <t>171gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1752,18 +1752,80 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17 bandi | 14 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 06/07/2026</t>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Formazione Continua - Quarta Edizione - Voucher aziendali a catalogo - P...</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Formazione 4.0</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>31/03/2027</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>261gg</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 13/07/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L20"/>
+  <autoFilter ref="A3:L21"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
@@ -1784,6 +1846,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1808,7 +1871,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 06/07/2026</t>
+          <t>DASHBOARD — 13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1927,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>25 gg</t>
+          <t>18 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -1891,7 +1954,7 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>25 gg</t>
+          <t>18 gg</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -633,7 +633,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 13/07/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 20/07/2026</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>18gg</t>
+          <t>11gg</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>18gg</t>
+          <t>11gg</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>79gg</t>
+          <t>72gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>144gg</t>
+          <t>137gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>352gg</t>
+          <t>345gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>536gg</t>
+          <t>529gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>CRITERI E MODALITA’ PER L’ASSEGNAZIONE DEI CONTRIBUTI PER L’ACQUISTO DI ...</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>72gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ricerca e Innovazione</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>171gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Formazione Continua - Quarta Edizione - Voucher aziendali a catalogo - P...</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Formazione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>261gg</t>
+          <t>164gg</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 13/07/2026</t>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 13/07/2026</t>
+          <t>DASHBOARD — 20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>18 gg</t>
+          <t>11 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>18 gg</t>
+          <t>11 gg</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -633,7 +633,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 20/07/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>11gg</t>
+          <t>4gg</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>11gg</t>
+          <t>4gg</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>72gg</t>
+          <t>65gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>137gg</t>
+          <t>130gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>345gg</t>
+          <t>338gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>529gg</t>
+          <t>522gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>CRITERI E MODALITA’ PER L’ASSEGNAZIONE DEI CONTRIBUTI PER L’ACQUISTO DI ...</t>
+          <t>Corso di Formazione per Aspirante Guida di Primo Livello - anno 2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>72gg</t>
+          <t>39gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>164gg</t>
+          <t>157gg</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 20/07/2026</t>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 20/07/2026</t>
+          <t>DASHBOARD — 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>11 gg</t>
+          <t>4 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>11 gg</t>
+          <t>4 gg</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,12 +71,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="005B21B6"/>
       <sz val="9"/>
     </font>
@@ -94,8 +88,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0092400E"/>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
       <sz val="10"/>
     </font>
     <font>
@@ -153,12 +147,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -193,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,35 +213,27 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -633,7 +619,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 27/07/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -804,14 +790,14 @@
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>4gg</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>IN SCADENZA</t>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>SCAD.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>CHIUSO</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -824,7 +810,7 @@
           <t>Solo chi ha versato acconto &gt;=20% entro 31/12/2025.</t>
         </is>
       </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -866,14 +852,14 @@
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>4gg</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>IN SCADENZA</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>SCAD.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>CHIUSO</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -930,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>65gg</t>
+          <t>58gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -948,7 +934,7 @@
           <t>Solo province Milano, Monza Brianza e Lodi.</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -992,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>130gg</t>
+          <t>123gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1072,7 +1058,7 @@
           <t>Sportello PMI aprira seconda meta 2026.</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1116,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1164,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1196,7 +1182,7 @@
           <t>Include AI, cloud, Industry 4.0.</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1240,7 +1226,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1302,7 +1288,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1316,7 +1302,7 @@
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1360,7 +1346,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1422,7 +1408,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1436,7 +1422,7 @@
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1480,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>338gg</t>
+          <t>331gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1542,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>522gg</t>
+          <t>515gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1560,7 +1546,7 @@
           <t>Rifinanziata con 650M euro per 2026-2027. Sportello continuo.</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1569,7 +1555,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Corso di Formazione per Aspirante Guida di Primo Livello - anno 2026</t>
+          <t>Manifestazione di interesse - Corsi di alta formazione per il personale ...</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1599,12 +1585,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>39gg</t>
+          <t>49gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1612,7 +1598,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1666,7 +1652,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1674,7 +1660,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1684,7 +1670,7 @@
           <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
@@ -1728,7 +1714,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1736,7 +1722,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1790,7 +1776,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>157gg</t>
+          <t>150gg</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1798,7 +1784,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1808,16 +1794,16 @@
           <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 2 in scadenza | 14 verificati manualmente | Aggiornato: 27/07/2026</t>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1871,107 +1857,57 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 27/07/2026</t>
+          <t>DASHBOARD — 03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>BANDI IN SCADENZA ENTRO 30 GIORNI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>BANDO</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ENTE</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>SCADENZA</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>GIORNI</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Credito d'Imposta Beni Strumentali 4.0</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>MIMIT / Agenzia delle Entrate</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>4 gg</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Apri bando</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Voucher Fiere e Mostre CCIAA Toscana NW 2026</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Camera di Commercio Toscana Nord-Ovest</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>4 gg</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>Apri bando</t>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Nessun bando in scadenza imminente questa settimana.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1991,283 +1927,283 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>LEGENDA E FONTI MONITORATE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>COLONNA FONTE</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr"/>
-      <c r="C3" s="19" t="inlineStr"/>
+      <c r="B3" s="17" t="inlineStr"/>
+      <c r="C3" s="17" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>OK (verde)</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Bando verificato manualmente su fonte ufficiale — affidabile</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr"/>
+      <c r="C4" s="17" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>AUTO (viola)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Trovato automaticamente via scraping — verificare prima dell'uso con clienti</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="19" t="inlineStr"/>
-      <c r="B6" s="19" t="inlineStr"/>
-      <c r="C6" s="19" t="inlineStr"/>
+      <c r="A6" s="17" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>COLONNA STATO</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr"/>
-      <c r="C7" s="19" t="inlineStr"/>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>APERTO (verde)</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Bando con scadenza futura &gt; 30 giorni</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>IN SCADENZA (giallo)</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Scadenza entro 30 giorni — agire subito</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>CHIUSO (rosso)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Bando scaduto (mostrato per 60 giorni poi rimosso)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
+      <c r="C10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="19" t="inlineStr"/>
+      <c r="A11" s="17" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr"/>
+      <c r="C11" s="17" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>FONTI MONITORATE</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr"/>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>FREQ.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Regione Toscana</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>regione.toscana.it / bandi FESR 2021-2027</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>bandi.regione.lombardia.it</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>MIMIT</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>mimit.gov.it/it/incentivi</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>SIMEST</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>simest.it (tutte le linee Fondo 394)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>CCIAA Toscana NW</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>tno.camcom.it/bandi (Lucca-Massa-Pisa)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>CCIAA Arezzo-Siena</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>as.camcom.it</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>CCIAA Firenze</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>fi.camcom.gov.it</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>EUIPO</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>euipo.europa.eu/sme-fund/2026</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>incentivi.gov.it</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Catalogo MIMIT (aggregatore ufficiale)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Agenzia Entrate</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Crediti d'imposta Formazione e Beni 4.0</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -619,7 +619,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 03/08/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 10/08/2026</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>58gg</t>
+          <t>51gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>123gg</t>
+          <t>116gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>331gg</t>
+          <t>324gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>515gg</t>
+          <t>508gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Manifestazione di interesse - Corsi di alta formazione per il personale ...</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Formazione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>49gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>143gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Ricerca e Innovazione</t>
+          <t>Avviso per il finanziamento dei percorsi di Istruzione e Formazione Prof...</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>150gg</t>
+          <t>255gg</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 03/08/2026</t>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 03/08/2026</t>
+          <t>DASHBOARD — 10/08/2026</t>
         </is>
       </c>
     </row>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -619,7 +619,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 10/08/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>51gg</t>
+          <t>44gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>116gg</t>
+          <t>109gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>324gg</t>
+          <t>317gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>508gg</t>
+          <t>501gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>143gg</t>
+          <t>136gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>255gg</t>
+          <t>248gg</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 10/08/2026</t>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 10/08/2026</t>
+          <t>DASHBOARD — 17/08/2026</t>
         </is>
       </c>
     </row>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -619,7 +619,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 17/08/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>44gg</t>
+          <t>37gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>109gg</t>
+          <t>102gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>317gg</t>
+          <t>310gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>501gg</t>
+          <t>494gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>136gg</t>
+          <t>129gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>248gg</t>
+          <t>241gg</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 17/08/2026</t>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 17/08/2026</t>
+          <t>DASHBOARD — 24/08/2026</t>
         </is>
       </c>
     </row>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="005B21B6"/>
       <sz val="9"/>
     </font>
@@ -88,8 +94,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="0094A3B8"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -147,12 +153,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -187,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,21 +225,29 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -619,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 24/08/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 31/08/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 14 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 13 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -695,37 +709,37 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Rafforza &amp; Innova 2025</t>
+          <t>Credito d'Imposta Beni Strumentali 4.0</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia / Finlombarda</t>
+          <t>MIMIT / Agenzia delle Entrate</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Innovazione / R&amp;S</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>30.000 euro (importo fisso)</t>
+          <t>Credito 20-40% investimento</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>100% fondo perduto</t>
+          <t>20% fino 2,5M / 10% fino 10M / 5% fino 20M euro</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -745,7 +759,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>URGENTE: scade 30/06/2026 ore 15:00</t>
+          <t>Solo chi ha versato acconto &gt;=20% entro 31/12/2025.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -757,32 +771,32 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Credito d'Imposta Beni Strumentali 4.0</t>
+          <t>Voucher Fiere e Mostre CCIAA Toscana NW 2026</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>MIMIT / Agenzia delle Entrate</t>
+          <t>Camera di Commercio Toscana Nord-Ovest</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>Regione Toscana</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>E-commerce &amp; Export</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Credito 20-40% investimento</t>
+          <t>Fino a 5.000 euro (extra UE) / 3.000 euro (Italia-UE)</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>20% fino 2,5M / 10% fino 10M / 5% fino 20M euro</t>
+          <t>50% fondo perduto</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -807,7 +821,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Solo chi ha versato acconto &gt;=20% entro 31/12/2025.</t>
+          <t>Solo province Lucca, Massa-Carrara e Pisa. Domanda via ReStart Infocamere.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -819,27 +833,27 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Voucher Fiere e Mostre CCIAA Toscana NW 2026</t>
+          <t>SPIDY — Speed up your business 2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Camera di Commercio Toscana Nord-Ovest</t>
+          <t>CCIAA Milano Monza Brianza Lodi</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Regione Toscana</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>E-commerce &amp; Export</t>
+          <t>Voucher Consulenza / Brand / UI-UX</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Fino a 5.000 euro (extra UE) / 3.000 euro (Italia-UE)</t>
+          <t>Da 2.500 a 18.000 euro</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -849,17 +863,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>SCAD.</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>CHIUSO</t>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>30gg</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -869,7 +883,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Solo province Lucca, Massa-Carrara e Pisa. Domanda via ReStart Infocamere.</t>
+          <t>Solo province Milano, Monza Brianza e Lodi.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -881,17 +895,17 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>SPIDY — Speed up your business 2026</t>
+          <t>EUIPO Fondo PMI 2026 — Voucher Brevetti</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>CCIAA Milano Monza Brianza Lodi</t>
+          <t>EUIPO / Commissione Europea / UIBM</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Regione Lombardia</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -901,22 +915,22 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Da 2.500 a 18.000 euro</t>
+          <t>Fino a 2.500 euro (cumulabile)</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>50% fondo perduto</t>
+          <t>75% marchi (max 700 eu) + 50-75% brevetti (max 2.500 eu)</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>37gg</t>
+          <t>95gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -931,7 +945,7 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Solo province Milano, Monza Brianza e Lodi.</t>
+          <t>Voucher 2 (Marchi): CHIUSO per esaurimento, riapertura attesa Q4 2026. Voucher 3 (Brevetti): APERTO.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -943,12 +957,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>EUIPO Fondo PMI 2026 — Voucher Brevetti</t>
+          <t>Voucher Cloud e Cybersecurity 2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>EUIPO / Commissione Europea / UIBM</t>
+          <t>MIMIT / Invitalia</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -958,27 +972,27 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Voucher Consulenza / Brand / UI-UX</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Fino a 2.500 euro (cumulabile)</t>
+          <t>Da 2.000 a 20.000 euro</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>75% marchi (max 700 eu) + 50-75% brevetti (max 2.500 eu)</t>
+          <t>50% fondo perduto</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>102gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -993,7 +1007,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Voucher 2 (Marchi): CHIUSO per esaurimento, riapertura attesa Q4 2026. Voucher 3 (Brevetti): APERTO.</t>
+          <t>Sportello PMI aprira seconda meta 2026.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -1005,32 +1019,32 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Voucher Cloud e Cybersecurity 2026</t>
+          <t>SIMEST Fondo 394 — E-commerce Internazionale</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>MIMIT / Invitalia</t>
+          <t>SIMEST (Gruppo CDP)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>SIMEST</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>E-commerce &amp; Export</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Da 2.000 a 20.000 euro</t>
+          <t>Fino a 500.000 euro</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>50% fondo perduto</t>
+          <t>Tasso 0,319% + fino 10% fondo perduto</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1040,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1055,7 +1069,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Sportello PMI aprira seconda meta 2026.</t>
+          <t>Richiede fatturato export min. 20% media biennale.</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -1067,7 +1081,7 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SIMEST Fondo 394 — E-commerce Internazionale</t>
+          <t>SIMEST Fondo 394 — Transizione Digitale ed Ecologica</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1082,12 +1096,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>E-commerce &amp; Export</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Fino a 500.000 euro</t>
+          <t>Fino a 2.500.000 euro</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1102,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1117,7 +1131,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Richiede fatturato export min. 20% media biennale.</t>
+          <t>Include AI, cloud, Industry 4.0.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -1129,7 +1143,7 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>SIMEST Fondo 394 — Transizione Digitale ed Ecologica</t>
+          <t>SIMEST Fondo 394 — Certificazioni e Consulenze</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1144,12 +1158,12 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Voucher Consulenza / Brand / UI-UX</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Fino a 2.500.000 euro</t>
+          <t>Fino a 120.000 euro</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -1164,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1179,7 +1193,7 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Include AI, cloud, Industry 4.0.</t>
+          <t>Cumulabile con altre linee SIMEST.</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -1191,32 +1205,32 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SIMEST Fondo 394 — Certificazioni e Consulenze</t>
+          <t>Transizione Digitale Imprese Lombarde</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SIMEST (Gruppo CDP)</t>
+          <t>Regione Lombardia — PR FESR 2021-2027</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SIMEST</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Voucher Consulenza / Brand / UI-UX</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Fino a 120.000 euro</t>
+          <t>Da 20.000 a 150.000 euro</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Tasso 0,319% + fino 10% fondo perduto</t>
+          <t>Fino al 50% fondo perduto</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1226,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1239,11 +1253,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Cumulabile con altre linee SIMEST.</t>
-        </is>
-      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -1253,17 +1263,17 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Transizione Digitale Imprese Lombarde</t>
+          <t>Servizi per l'Innovazione — Impresa Digitale</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Regione Lombardia — PR FESR 2021-2027</t>
+          <t>Regione Toscana — PR FESR 2021-2027</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Regione Lombardia</t>
+          <t>Regione Toscana</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1273,12 +1283,12 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Da 20.000 a 150.000 euro</t>
+          <t>Fino a 150.000 euro</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Fino al 50% fondo perduto</t>
+          <t>Fino al 70% fondo perduto</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1288,7 +1298,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1301,7 +1311,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Verificare disponibilita risorse e stato sportello.</t>
+        </is>
+      </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -1311,32 +1325,32 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Servizi per l'Innovazione — Impresa Digitale</t>
+          <t>Credito d'Imposta Formazione 4.0</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Regione Toscana — PR FESR 2021-2027</t>
+          <t>Agenzia delle Entrate</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Regione Toscana</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Fino a 150.000 euro</t>
+          <t>Credito 10-70% spese formazione</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Fino al 70% fondo perduto</t>
+          <t>70% micro / 50% piccole / 30% medie imprese</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1346,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1359,11 +1373,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Verificare disponibilita risorse e stato sportello.</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -1373,17 +1383,17 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Credito d'Imposta Formazione 4.0</t>
+          <t>Competenze &amp; Innovazione II edizione</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Agenzia delle Entrate</t>
+          <t>Regione Lombardia / Unioncamere</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1393,22 +1403,22 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Credito 10-70% spese formazione</t>
+          <t>Fino a 50.000 euro</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>70% micro / 50% piccole / 30% medie imprese</t>
+          <t>80% fondo perduto</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>30/06/2027</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>303gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1421,7 +1431,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Investimento minimo 10.000 euro.</t>
+        </is>
+      </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -1431,42 +1445,42 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Competenze &amp; Innovazione II edizione</t>
+          <t>Nuova Sabatini — Beni Strumentali e Digitalizzazione 4.0</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia / Unioncamere</t>
+          <t>MIMIT / Banche convenzionate</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Formazione 4.0</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Fino a 50.000 euro</t>
+          <t>Da 20.000 a 4.000.000 euro</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>80% fondo perduto</t>
+          <t>Contributo in conto interessi + tasso agevolato</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>30/06/2027</t>
+          <t>31/12/2027</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>310gg</t>
+          <t>487gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Investimento minimo 10.000 euro.</t>
+          <t>Rifinanziata con 650M euro per 2026-2027. Sportello continuo.</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -1493,17 +1507,17 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Nuova Sabatini — Beni Strumentali e Digitalizzazione 4.0</t>
+          <t>BANDO PER LA PARTECIPAZIONE ALLE INIZIATIVE DI PROMOZIONE TURISTICA SUI ...</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>MIMIT / Banche convenzionate</t>
+          <t>Regione Lombardia Bandi</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1513,37 +1527,37 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Da 20.000 a 4.000.000 euro</t>
+          <t>Vedere bando</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Contributo in conto interessi + tasso agevolato</t>
+          <t>Vedere bando</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>31/12/2027</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>494gg</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>15gg</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Rifinanziata con 650M euro per 2026-2027. Sportello continuo.</t>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -1590,7 +1604,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1598,7 +1612,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1652,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1660,7 +1674,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1714,7 +1728,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>129gg</t>
+          <t>122gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1722,7 +1736,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1738,80 +1752,18 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Avviso per il finanziamento dei percorsi di Istruzione e Formazione Prof...</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Formazione 4.0</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2027</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>241gg</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 0 in scadenza | 14 verificati manualmente | Aggiornato: 24/08/2026</t>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17 bandi | 13 aperti | 2 in scadenza | 13 verificati manualmente | Aggiornato: 31/08/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L21"/>
+  <autoFilter ref="A3:L20"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
@@ -1832,7 +1784,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1844,7 +1795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1857,57 +1808,107 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 24/08/2026</t>
+          <t>DASHBOARD — 31/08/2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>BANDI IN SCADENZA ENTRO 30 GIORNI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>BANDO</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ENTE</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>SCADENZA</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>GIORNI</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Nessun bando in scadenza imminente questa settimana.</t>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>BANDO PER LA PARTECIPAZIONE ALLE INIZIATIVE DI PROMOZIONE TURISTICA SUI ...</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>15 gg</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>SPIDY — Speed up your business 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>CCIAA Milano Monza Brianza Lodi</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>30 gg</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1927,283 +1928,283 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>LEGENDA E FONTI MONITORATE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>COLONNA FONTE</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr"/>
-      <c r="C3" s="17" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr"/>
+      <c r="C3" s="19" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>OK (verde)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Bando verificato manualmente su fonte ufficiale — affidabile</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr"/>
+      <c r="C4" s="19" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>AUTO (viola)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Trovato automaticamente via scraping — verificare prima dell'uso con clienti</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr"/>
+      <c r="C5" s="19" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr"/>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr"/>
+      <c r="A6" s="19" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>COLONNA STATO</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>APERTO (verde)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Bando con scadenza futura &gt; 30 giorni</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>IN SCADENZA (giallo)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Scadenza entro 30 giorni — agire subito</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>CHIUSO (rosso)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Bando scaduto (mostrato per 60 giorni poi rimosso)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="17" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr"/>
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>FONTI MONITORATE</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>FREQ.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Regione Toscana</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>regione.toscana.it / bandi FESR 2021-2027</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>bandi.regione.lombardia.it</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>MIMIT</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>mimit.gov.it/it/incentivi</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>SIMEST</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>simest.it (tutte le linee Fondo 394)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>CCIAA Toscana NW</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>tno.camcom.it/bandi (Lucca-Massa-Pisa)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>CCIAA Arezzo-Siena</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>as.camcom.it</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CCIAA Firenze</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>fi.camcom.gov.it</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>EUIPO</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>euipo.europa.eu/sme-fund/2026</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>incentivi.gov.it</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Catalogo MIMIT (aggregatore ufficiale)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Agenzia Entrate</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Crediti d'imposta Formazione e Beni 4.0</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -633,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 31/08/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 07/09/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 13 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 13 bandi verificati + 5 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>30gg</t>
+          <t>23gg</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>95gg</t>
+          <t>88gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>303gg</t>
+          <t>296gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>487gg</t>
+          <t>480gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>BANDO PER LA PARTECIPAZIONE ALLE INIZIATIVE DI PROMOZIONE TURISTICA SUI ...</t>
+          <t>Bando Export su Misura 2026: Servizi a supporto delle imprese per l’acce...</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>E-commerce &amp; Export</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>15gg</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>IN SCADENZA</t>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>32gg</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Offerta formativa di corsi annuali di Istruzione e Formazione Profession...</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>53gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>122gg</t>
+          <t>115gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1693,77 +1693,139 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Istruzione, Formazione e Lavoro</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>115gg</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>Ricerca e Innovazione</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Regione Lombardia Bandi</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Vedere bando</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Vedere bando</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>122gg</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>115gg</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17 bandi | 13 aperti | 2 in scadenza | 13 verificati manualmente | Aggiornato: 31/08/2026</t>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18 bandi | 15 aperti | 1 in scadenza | 13 verificati manualmente | Aggiornato: 07/09/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L20"/>
+  <autoFilter ref="A3:L21"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
@@ -1784,6 +1846,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1795,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1808,7 +1871,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 31/08/2026</t>
+          <t>DASHBOARD — 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1849,52 +1912,25 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>BANDO PER LA PARTECIPAZIONE ALLE INIZIATIVE DI PROMOZIONE TURISTICA SUI ...</t>
+          <t>SPIDY — Speed up your business 2026</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Regione Lombardia Bandi</t>
+          <t>CCIAA Milano Monza Brianza Lodi</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>15 gg</t>
+          <t>23 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Apri bando</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>SPIDY — Speed up your business 2026</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>CCIAA Milano Monza Brianza Lodi</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>30 gg</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Apri bando</t>
         </is>
@@ -1907,7 +1943,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -633,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 07/09/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 13 bandi verificati + 5 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 13 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>23gg</t>
+          <t>16gg</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>88gg</t>
+          <t>81gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>296gg</t>
+          <t>289gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>480gg</t>
+          <t>473gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1540,14 +1540,14 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>32gg</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>25gg</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Offerta formativa di corsi annuali di Istruzione e Formazione Profession...</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Formazione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>53gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>115gg</t>
+          <t>108gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1752,80 +1752,18 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ricerca e Innovazione</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>115gg</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18 bandi | 15 aperti | 1 in scadenza | 13 verificati manualmente | Aggiornato: 07/09/2026</t>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17 bandi | 13 aperti | 2 in scadenza | 13 verificati manualmente | Aggiornato: 14/09/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L21"/>
+  <autoFilter ref="A3:L20"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
@@ -1846,7 +1784,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1858,7 +1795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1871,7 +1808,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 07/09/2026</t>
+          <t>DASHBOARD — 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1864,37 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>23 gg</t>
+          <t>16 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Bando Export su Misura 2026: Servizi a supporto delle imprese per l’acce...</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>25 gg</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Apri bando</t>
         </is>
@@ -1943,6 +1907,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -633,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 14/09/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 13 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 13 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>16gg</t>
+          <t>9gg</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>81gg</t>
+          <t>74gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>289gg</t>
+          <t>282gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>473gg</t>
+          <t>466gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Bando Export su Misura 2026: Servizi a supporto delle imprese per l’acce...</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>E-commerce &amp; Export</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>25gg</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>IN SCADENZA</t>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>101gg</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>108gg</t>
+          <t>101gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1690,80 +1690,18 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Ricerca e Innovazione</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>108gg</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17 bandi | 13 aperti | 2 in scadenza | 13 verificati manualmente | Aggiornato: 14/09/2026</t>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  16 bandi | 13 aperti | 1 in scadenza | 13 verificati manualmente | Aggiornato: 21/09/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L20"/>
+  <autoFilter ref="A3:L19"/>
   <mergeCells count="3">
+    <mergeCell ref="A20:L20"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
@@ -1783,7 +1721,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1795,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1808,7 +1745,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 14/09/2026</t>
+          <t>DASHBOARD — 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1801,10 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>16 gg</t>
+          <t>9 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Apri bando</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Bando Export su Misura 2026: Servizi a supporto delle imprese per l’acce...</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>25 gg</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Apri bando</t>
         </is>
@@ -1907,7 +1817,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -633,7 +633,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 21/09/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>9gg</t>
+          <t>2gg</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>74gg</t>
+          <t>67gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>282gg</t>
+          <t>275gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>466gg</t>
+          <t>459gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>101gg</t>
+          <t>94gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  16 bandi | 13 aperti | 1 in scadenza | 13 verificati manualmente | Aggiornato: 21/09/2026</t>
+          <t xml:space="preserve">  16 bandi | 13 aperti | 1 in scadenza | 13 verificati manualmente | Aggiornato: 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 21/09/2026</t>
+          <t>DASHBOARD — 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>9 gg</t>
+          <t>2 gg</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,12 +71,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="005B21B6"/>
       <sz val="9"/>
     </font>
@@ -94,8 +88,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0092400E"/>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
       <sz val="10"/>
     </font>
     <font>
@@ -153,12 +147,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -193,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -225,29 +219,21 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -613,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -633,14 +619,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 28/09/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 05/10/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 13 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 11 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -709,37 +695,37 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Credito d'Imposta Beni Strumentali 4.0</t>
+          <t>SPIDY — Speed up your business 2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>MIMIT / Agenzia delle Entrate</t>
+          <t>CCIAA Milano Monza Brianza Lodi</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Voucher Consulenza / Brand / UI-UX</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Credito 20-40% investimento</t>
+          <t>Da 2.500 a 18.000 euro</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>20% fino 2,5M / 10% fino 10M / 5% fino 20M euro</t>
+          <t>50% fondo perduto</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -759,7 +745,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Solo chi ha versato acconto &gt;=20% entro 31/12/2025.</t>
+          <t>Solo province Milano, Monza Brianza e Lodi.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -771,47 +757,47 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Voucher Fiere e Mostre CCIAA Toscana NW 2026</t>
+          <t>EUIPO Fondo PMI 2026 — Voucher Brevetti</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Camera di Commercio Toscana Nord-Ovest</t>
+          <t>EUIPO / Commissione Europea / UIBM</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Regione Toscana</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>E-commerce &amp; Export</t>
+          <t>Voucher Consulenza / Brand / UI-UX</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Fino a 5.000 euro (extra UE) / 3.000 euro (Italia-UE)</t>
+          <t>Fino a 2.500 euro (cumulabile)</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>50% fondo perduto</t>
+          <t>75% marchi (max 700 eu) + 50-75% brevetti (max 2.500 eu)</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>SCAD.</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>CHIUSO</t>
+          <t>60gg</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -821,7 +807,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Solo province Lucca, Massa-Carrara e Pisa. Domanda via ReStart Infocamere.</t>
+          <t>Voucher 2 (Marchi): CHIUSO per esaurimento, riapertura attesa Q4 2026. Voucher 3 (Brevetti): APERTO.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -833,27 +819,27 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SPIDY — Speed up your business 2026</t>
+          <t>Voucher Cloud e Cybersecurity 2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CCIAA Milano Monza Brianza Lodi</t>
+          <t>MIMIT / Invitalia</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Voucher Consulenza / Brand / UI-UX</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Da 2.500 a 18.000 euro</t>
+          <t>Da 2.000 a 20.000 euro</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -863,17 +849,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>2gg</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>IN SCADENZA</t>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>87gg</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -883,7 +869,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Solo province Milano, Monza Brianza e Lodi.</t>
+          <t>Sportello PMI aprira seconda meta 2026.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -895,42 +881,42 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>EUIPO Fondo PMI 2026 — Voucher Brevetti</t>
+          <t>SIMEST Fondo 394 — E-commerce Internazionale</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>EUIPO / Commissione Europea / UIBM</t>
+          <t>SIMEST (Gruppo CDP)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>SIMEST</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Voucher Consulenza / Brand / UI-UX</t>
+          <t>E-commerce &amp; Export</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Fino a 2.500 euro (cumulabile)</t>
+          <t>Fino a 500.000 euro</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>75% marchi (max 700 eu) + 50-75% brevetti (max 2.500 eu)</t>
+          <t>Tasso 0,319% + fino 10% fondo perduto</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>67gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -945,7 +931,7 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Voucher 2 (Marchi): CHIUSO per esaurimento, riapertura attesa Q4 2026. Voucher 3 (Brevetti): APERTO.</t>
+          <t>Richiede fatturato export min. 20% media biennale.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -957,32 +943,32 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Voucher Cloud e Cybersecurity 2026</t>
+          <t>SIMEST Fondo 394 — Transizione Digitale ed Ecologica</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>MIMIT / Invitalia</t>
+          <t>SIMEST (Gruppo CDP)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>SIMEST</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Da 2.000 a 20.000 euro</t>
+          <t>Fino a 2.500.000 euro</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>50% fondo perduto</t>
+          <t>Tasso 0,319% + fino 10% fondo perduto</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -992,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1007,7 +993,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Sportello PMI aprira seconda meta 2026.</t>
+          <t>Include AI, cloud, Industry 4.0.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -1019,7 +1005,7 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>SIMEST Fondo 394 — E-commerce Internazionale</t>
+          <t>SIMEST Fondo 394 — Certificazioni e Consulenze</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1034,12 +1020,12 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>E-commerce &amp; Export</t>
+          <t>Voucher Consulenza / Brand / UI-UX</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Fino a 500.000 euro</t>
+          <t>Fino a 120.000 euro</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1054,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1069,7 +1055,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Richiede fatturato export min. 20% media biennale.</t>
+          <t>Cumulabile con altre linee SIMEST.</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -1081,17 +1067,17 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SIMEST Fondo 394 — Transizione Digitale ed Ecologica</t>
+          <t>Transizione Digitale Imprese Lombarde</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SIMEST (Gruppo CDP)</t>
+          <t>Regione Lombardia — PR FESR 2021-2027</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SIMEST</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1101,12 +1087,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Fino a 2.500.000 euro</t>
+          <t>Da 20.000 a 150.000 euro</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Tasso 0,319% + fino 10% fondo perduto</t>
+          <t>Fino al 50% fondo perduto</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1116,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1129,11 +1115,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Include AI, cloud, Industry 4.0.</t>
-        </is>
-      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -1143,32 +1125,32 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>SIMEST Fondo 394 — Certificazioni e Consulenze</t>
+          <t>Servizi per l'Innovazione — Impresa Digitale</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SIMEST (Gruppo CDP)</t>
+          <t>Regione Toscana — PR FESR 2021-2027</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>SIMEST</t>
+          <t>Regione Toscana</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Voucher Consulenza / Brand / UI-UX</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Fino a 120.000 euro</t>
+          <t>Fino a 150.000 euro</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Tasso 0,319% + fino 10% fondo perduto</t>
+          <t>Fino al 70% fondo perduto</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1178,7 +1160,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1193,7 +1175,7 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Cumulabile con altre linee SIMEST.</t>
+          <t>Verificare disponibilita risorse e stato sportello.</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -1205,32 +1187,32 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Transizione Digitale Imprese Lombarde</t>
+          <t>Credito d'Imposta Formazione 4.0</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia — PR FESR 2021-2027</t>
+          <t>Agenzia delle Entrate</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Regione Lombardia</t>
+          <t>Nazionale</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Da 20.000 a 150.000 euro</t>
+          <t>Credito 10-70% spese formazione</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Fino al 50% fondo perduto</t>
+          <t>70% micro / 50% piccole / 30% medie imprese</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1240,7 +1222,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1263,42 +1245,42 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Servizi per l'Innovazione — Impresa Digitale</t>
+          <t>Competenze &amp; Innovazione II edizione</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Regione Toscana — PR FESR 2021-2027</t>
+          <t>Regione Lombardia / Unioncamere</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Regione Toscana</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Fino a 150.000 euro</t>
+          <t>Fino a 50.000 euro</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Fino al 70% fondo perduto</t>
+          <t>80% fondo perduto</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>30/06/2027</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>268gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1313,7 +1295,7 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Verificare disponibilita risorse e stato sportello.</t>
+          <t>Investimento minimo 10.000 euro.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -1325,12 +1307,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Credito d'Imposta Formazione 4.0</t>
+          <t>Nuova Sabatini — Beni Strumentali e Digitalizzazione 4.0</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Agenzia delle Entrate</t>
+          <t>MIMIT / Banche convenzionate</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1340,27 +1322,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Formazione 4.0</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Credito 10-70% spese formazione</t>
+          <t>Da 20.000 a 4.000.000 euro</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>70% micro / 50% piccole / 30% medie imprese</t>
+          <t>Contributo in conto interessi + tasso agevolato</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>31/12/2027</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>452gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1373,7 +1355,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Rifinanziata con 650M euro per 2026-2027. Sportello continuo.</t>
+        </is>
+      </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -1383,12 +1369,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Competenze &amp; Innovazione II edizione</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Regione Lombardia / Unioncamere</t>
+          <t>Regione Lombardia Bandi</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1398,27 +1384,27 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Formazione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Fino a 50.000 euro</t>
+          <t>Vedere bando</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>80% fondo perduto</t>
+          <t>Vedere bando</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>30/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>275gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1426,14 +1412,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Investimento minimo 10.000 euro.</t>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -1445,42 +1431,42 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nuova Sabatini — Beni Strumentali e Digitalizzazione 4.0</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>MIMIT / Banche convenzionate</t>
+          <t>Regione Lombardia Bandi</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Nazionale</t>
+          <t>Regione Lombardia</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Da 20.000 a 4.000.000 euro</t>
+          <t>Vedere bando</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Contributo in conto interessi + tasso agevolato</t>
+          <t>Vedere bando</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>31/12/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>459gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1488,14 +1474,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Rifinanziata con 650M euro per 2026-2027. Sportello continuo.</t>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -1507,7 +1493,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1542,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>87gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1550,7 +1536,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1569,7 +1555,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Contributo abbattimento interessi sull’iniziativa "Finanziamento per il ...</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1584,7 +1570,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1599,12 +1585,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>30/04/2027</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>94gg</t>
+          <t>207gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1612,7 +1598,7 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1628,79 +1614,17 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Ricerca e Innovazione</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>94gg</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  16 bandi | 13 aperti | 1 in scadenza | 13 verificati manualmente | Aggiornato: 28/09/2026</t>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  15 bandi | 14 aperti | 0 in scadenza | 11 verificati manualmente | Aggiornato: 05/10/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L19"/>
+  <autoFilter ref="A3:L18"/>
   <mergeCells count="3">
-    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -1720,7 +1644,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1745,79 +1668,57 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 28/09/2026</t>
+          <t>DASHBOARD — 05/10/2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>BANDI IN SCADENZA ENTRO 30 GIORNI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>BANDO</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ENTE</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>SCADENZA</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>GIORNI</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>SPIDY — Speed up your business 2026</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>CCIAA Milano Monza Brianza Lodi</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>2 gg</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Apri bando</t>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Nessun bando in scadenza imminente questa settimana.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1837,283 +1738,283 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>LEGENDA E FONTI MONITORATE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>COLONNA FONTE</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr"/>
-      <c r="C3" s="19" t="inlineStr"/>
+      <c r="B3" s="17" t="inlineStr"/>
+      <c r="C3" s="17" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>OK (verde)</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Bando verificato manualmente su fonte ufficiale — affidabile</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr"/>
+      <c r="C4" s="17" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>AUTO (viola)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Trovato automaticamente via scraping — verificare prima dell'uso con clienti</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="19" t="inlineStr"/>
-      <c r="B6" s="19" t="inlineStr"/>
-      <c r="C6" s="19" t="inlineStr"/>
+      <c r="A6" s="17" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>COLONNA STATO</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr"/>
-      <c r="C7" s="19" t="inlineStr"/>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>APERTO (verde)</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Bando con scadenza futura &gt; 30 giorni</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>IN SCADENZA (giallo)</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Scadenza entro 30 giorni — agire subito</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>CHIUSO (rosso)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Bando scaduto (mostrato per 60 giorni poi rimosso)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
+      <c r="C10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="19" t="inlineStr"/>
+      <c r="A11" s="17" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr"/>
+      <c r="C11" s="17" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>FONTI MONITORATE</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr"/>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>FREQ.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Regione Toscana</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>regione.toscana.it / bandi FESR 2021-2027</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>bandi.regione.lombardia.it</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>MIMIT</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>mimit.gov.it/it/incentivi</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>SIMEST</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>simest.it (tutte le linee Fondo 394)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>CCIAA Toscana NW</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>tno.camcom.it/bandi (Lucca-Massa-Pisa)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>CCIAA Arezzo-Siena</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>as.camcom.it</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>CCIAA Firenze</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>fi.camcom.gov.it</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>EUIPO</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>euipo.europa.eu/sme-fund/2026</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>incentivi.gov.it</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Catalogo MIMIT (aggregatore ufficiale)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Agenzia Entrate</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Crediti d'imposta Formazione e Beni 4.0</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -619,7 +619,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 05/10/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 12/10/2026</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>60gg</t>
+          <t>53gg</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>268gg</t>
+          <t>261gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>452gg</t>
+          <t>445gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Bando rivolto agli enti locali per il contributo finalizzato all'acquisi...</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>12/11/2026</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>31gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Ricerca e Innovazione</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>87gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Contributo abbattimento interessi sull’iniziativa "Finanziamento per il ...</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>30/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>207gg</t>
+          <t>80gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15 bandi | 14 aperti | 0 in scadenza | 11 verificati manualmente | Aggiornato: 05/10/2026</t>
+          <t xml:space="preserve">  15 bandi | 14 aperti | 0 in scadenza | 11 verificati manualmente | Aggiornato: 12/10/2026</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 05/10/2026</t>
+          <t>DASHBOARD — 12/10/2026</t>
         </is>
       </c>
     </row>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -619,14 +619,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 12/10/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 19/10/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 11 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 11 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>53gg</t>
+          <t>46gg</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>261gg</t>
+          <t>254gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>445gg</t>
+          <t>438gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Bando rivolto agli enti locali per il contributo finalizzato all'acquisi...</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Digitalizzazione / Transizione 4.0</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>31gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>80gg</t>
+          <t>73gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1552,81 +1552,19 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Ricerca e Innovazione</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Regione Lombardia Bandi</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Regione Lombardia</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Vedere bando</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>80gg</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  15 bandi | 14 aperti | 0 in scadenza | 11 verificati manualmente | Aggiornato: 12/10/2026</t>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14 bandi | 13 aperti | 0 in scadenza | 11 verificati manualmente | Aggiornato: 19/10/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L18"/>
+  <autoFilter ref="A3:L17"/>
   <mergeCells count="3">
-    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A18:L18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId1"/>
@@ -1643,7 +1581,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1668,7 +1605,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 12/10/2026</t>
+          <t>DASHBOARD — 19/10/2026</t>
         </is>
       </c>
     </row>

--- a/output/BandiRadar.xlsx
+++ b/output/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="005B21B6"/>
       <sz val="9"/>
     </font>
@@ -88,8 +94,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="0094A3B8"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -147,12 +153,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -187,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,21 +225,29 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -619,14 +633,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 19/10/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 11 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 11 bandi verificati + 6 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -792,7 +806,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>46gg</t>
+          <t>39gg</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -854,7 +868,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -916,7 +930,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +992,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1054,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1116,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1160,7 +1174,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1222,7 +1236,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>73gg</t>
+          <t>66gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1280,7 +1294,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>254gg</t>
+          <t>247gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1342,7 +1356,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>438gg</t>
+          <t>431gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1369,7 +1383,7 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>FORMAZIONE NEGLI AMBITI PROFESSIONALI DEL RESTAURO DEI BENI CULTURALI E ...</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1384,7 +1398,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1399,20 +1413,20 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>73gg</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>3gg</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1431,7 +1445,7 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>INFORMAZIONE E ASSISTENZA ALLE VITTIME: IL DIRITTO DI COMPRENDERE E DI E...</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1446,7 +1460,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Formazione 4.0</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1461,20 +1475,20 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>73gg</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
+          <t>13/11/2026</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>18gg</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
@@ -1493,78 +1507,264 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>Contributo regionale per la redazione o revisione dei Piani comunali di ...</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Digitalizzazione / Transizione 4.0</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>23/11/2026</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>28gg</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>IN SCADENZA</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Attività Produttive/Imprese</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>66gg</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Istruzione, Formazione e Lavoro</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>66gg</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>Ricerca e Innovazione</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Regione Lombardia Bandi</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Vedere bando</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Vedere bando</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>73gg</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>66gg</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  14 bandi | 13 aperti | 0 in scadenza | 11 verificati manualmente | Aggiornato: 19/10/2026</t>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17 bandi | 13 aperti | 3 in scadenza | 11 verificati manualmente | Aggiornato: 26/10/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L17"/>
+  <autoFilter ref="A3:L20"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A18:L18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId1"/>
@@ -1581,6 +1781,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1592,7 +1795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1605,57 +1808,135 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 19/10/2026</t>
+          <t>DASHBOARD — 26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>BANDI IN SCADENZA ENTRO 30 GIORNI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>BANDO</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ENTE</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>SCADENZA</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>GIORNI</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Nessun bando in scadenza imminente questa settimana.</t>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>FORMAZIONE NEGLI AMBITI PROFESSIONALI DEL RESTAURO DEI BENI CULTURALI E ...</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>3 gg</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>INFORMAZIONE E ASSISTENZA ALLE VITTIME: IL DIRITTO DI COMPRENDERE E DI E...</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>13/11/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>18 gg</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Contributo regionale per la redazione o revisione dei Piani comunali di ...</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>23/11/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>28 gg</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Apri bando</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1675,283 +1956,283 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>LEGENDA E FONTI MONITORATE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>COLONNA FONTE</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr"/>
-      <c r="C3" s="17" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr"/>
+      <c r="C3" s="19" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>OK (verde)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Bando verificato manualmente su fonte ufficiale — affidabile</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr"/>
+      <c r="C4" s="19" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>AUTO (viola)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Trovato automaticamente via scraping — verificare prima dell'uso con clienti</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr"/>
+      <c r="C5" s="19" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr"/>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr"/>
+      <c r="A6" s="19" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>COLONNA STATO</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>APERTO (verde)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Bando con scadenza futura &gt; 30 giorni</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>IN SCADENZA (giallo)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Scadenza entro 30 giorni — agire subito</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>CHIUSO (rosso)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Bando scaduto (mostrato per 60 giorni poi rimosso)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="17" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr"/>
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>FONTI MONITORATE</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>FREQ.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Regione Toscana</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>regione.toscana.it / bandi FESR 2021-2027</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>bandi.regione.lombardia.it</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>MIMIT</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>mimit.gov.it/it/incentivi</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>SIMEST</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>simest.it (tutte le linee Fondo 394)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>CCIAA Toscana NW</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>tno.camcom.it/bandi (Lucca-Massa-Pisa)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>CCIAA Arezzo-Siena</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>as.camcom.it</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CCIAA Firenze</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>fi.camcom.gov.it</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>EUIPO</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>euipo.europa.eu/sme-fund/2026</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>incentivi.gov.it</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Catalogo MIMIT (aggregatore ufficiale)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Agenzia Entrate</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Crediti d'imposta Formazione e Beni 4.0</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Mens.</t>
         </is>
